--- a/output/catalogo_csv_validos.xlsx
+++ b/output/catalogo_csv_validos.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Links API" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Links" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="90" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>anime_slug_used</t>
+          <t>query_used</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
